--- a/XLibur.Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -477,7 +477,7 @@
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="22.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20.567768" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="21.424911" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:3">

--- a/XLibur.Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -622,8 +622,9 @@
       <x:c r="B22" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C22" s="0">
+      <x:c r="C22" s="0" t="e">
         <x:f>1/0</x:f>
+        <x:v>#DIV/0!</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
